--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.73</v>
+        <v>1.12</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.11</v>
+        <v>7.1</v>
       </c>
       <c r="R64" t="n">
-        <v>5.18</v>
+        <v>13</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,16 +13060,16 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>7.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="R70" t="n">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.83</v>
+        <v>7.65</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="R97" t="n">
-        <v>4.22</v>
+        <v>1.48</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.85</v>
+        <v>3.04</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.08</v>
+        <v>3.44</v>
       </c>
       <c r="R102" t="n">
-        <v>3.89</v>
+        <v>2.53</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.44</v>
+        <v>4.96</v>
       </c>
       <c r="R114" t="n">
-        <v>3.89</v>
+        <v>8.25</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34336,10 +34336,10 @@
         <v>0</v>
       </c>
       <c r="AE172" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF172" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG172" t="n">
         <v>0</v>
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF174" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF190" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.19</v>
+        <v>3.8</v>
       </c>
       <c r="R192" t="n">
-        <v>4.62</v>
+        <v>3.8</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AF192" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q193" t="n">
-        <v>5.43</v>
+        <v>3.19</v>
       </c>
       <c r="R193" t="n">
-        <v>8.800000000000001</v>
+        <v>4.62</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AF193" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.8</v>
+        <v>5.43</v>
       </c>
       <c r="R194" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AF194" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF197" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39458,10 +39458,10 @@
         <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF198" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>6.29</v>
+        <v>1.96</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.92</v>
+        <v>3.38</v>
       </c>
       <c r="R204" t="n">
-        <v>1.53</v>
+        <v>3.83</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.96</v>
+        <v>10.1</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.38</v>
+        <v>5.35</v>
       </c>
       <c r="R212" t="n">
-        <v>3.83</v>
+        <v>1.28</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF241" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF242" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48230,22 +48230,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48821,22 +48821,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q253" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF253" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,55 +51824,55 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>3.4</v>
+        <v>5.26</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R261" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="n">
+        <v>0</v>
+      </c>
+      <c r="V261" t="n">
+        <v>0</v>
+      </c>
+      <c r="W261" t="n">
+        <v>0</v>
+      </c>
+      <c r="X261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF261" t="n">
         <v>2.05</v>
-      </c>
-      <c r="S261" t="n">
-        <v>0</v>
-      </c>
-      <c r="T261" t="n">
-        <v>0</v>
-      </c>
-      <c r="U261" t="n">
-        <v>0</v>
-      </c>
-      <c r="V261" t="n">
-        <v>0</v>
-      </c>
-      <c r="W261" t="n">
-        <v>0</v>
-      </c>
-      <c r="X261" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y261" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE261" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF261" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>5.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q262" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R262" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52066,10 +52066,10 @@
         <v>0</v>
       </c>
       <c r="AE262" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF262" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54582,13 +54582,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q275" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AE275" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF275" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG275" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF277" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q282" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R282" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,10 +56006,10 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF282" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG282" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G288" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.32</v>
+        <v>2.82</v>
       </c>
       <c r="R56" t="n">
-        <v>3.21</v>
+        <v>2.53</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>7.55</v>
+        <v>1.98</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.15</v>
+        <v>4</v>
       </c>
       <c r="R67" t="n">
-        <v>1.35</v>
+        <v>3.29</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R68" t="n">
-        <v>3.29</v>
+        <v>2.65</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.38</v>
+        <v>7.55</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.8</v>
+        <v>5.15</v>
       </c>
       <c r="R70" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.82</v>
+        <v>4.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R73" t="n">
-        <v>3.65</v>
+        <v>1.68</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14839,10 +14839,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R90" t="n">
-        <v>1.8</v>
+        <v>5.86</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.69</v>
+        <v>7.65</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>5.86</v>
+        <v>1.48</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>7.65</v>
+        <v>3.04</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="R97" t="n">
-        <v>1.48</v>
+        <v>2.53</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.08</v>
+        <v>3.87</v>
       </c>
       <c r="R100" t="n">
-        <v>3.89</v>
+        <v>4.22</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="R102" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.44</v>
+        <v>4.96</v>
       </c>
       <c r="R113" t="n">
-        <v>3.89</v>
+        <v>8.25</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R121" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="R122" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q171" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="R171" t="n">
-        <v>2.68</v>
+        <v>3.86</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34336,10 +34336,10 @@
         <v>0</v>
       </c>
       <c r="AE172" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF172" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG172" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>8.199999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="Q174" t="n">
-        <v>5.73</v>
+        <v>3.73</v>
       </c>
       <c r="R174" t="n">
-        <v>1.32</v>
+        <v>2.86</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF174" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF179" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.82</v>
+        <v>1.6</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.11</v>
+        <v>4.53</v>
       </c>
       <c r="R180" t="n">
-        <v>2.51</v>
+        <v>5.9</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF190" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39655,10 +39655,10 @@
         <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF199" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.09</v>
+        <v>10.1</v>
       </c>
       <c r="Q210" t="n">
-        <v>9.199999999999999</v>
+        <v>5.35</v>
       </c>
       <c r="R210" t="n">
-        <v>22</v>
+        <v>1.28</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.52</v>
+        <v>6.2</v>
       </c>
       <c r="R211" t="n">
-        <v>4.47</v>
+        <v>11.5</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>10.1</v>
+        <v>6.29</v>
       </c>
       <c r="Q212" t="n">
-        <v>5.35</v>
+        <v>3.92</v>
       </c>
       <c r="R212" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>6.29</v>
+        <v>1.42</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.92</v>
+        <v>4.86</v>
       </c>
       <c r="R213" t="n">
-        <v>1.53</v>
+        <v>9.4</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF213" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q215" t="n">
-        <v>6.2</v>
+        <v>3.52</v>
       </c>
       <c r="R215" t="n">
-        <v>11.5</v>
+        <v>4.47</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,22 +48230,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF243" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48821,22 +48821,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>5.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q261" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R261" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -51869,10 +51869,10 @@
         <v>0</v>
       </c>
       <c r="AE261" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF261" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,55 +52021,55 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>3.4</v>
+        <v>5.26</v>
       </c>
       <c r="Q262" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R262" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="n">
+        <v>0</v>
+      </c>
+      <c r="V262" t="n">
+        <v>0</v>
+      </c>
+      <c r="W262" t="n">
+        <v>0</v>
+      </c>
+      <c r="X262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF262" t="n">
         <v>2.05</v>
-      </c>
-      <c r="S262" t="n">
-        <v>0</v>
-      </c>
-      <c r="T262" t="n">
-        <v>0</v>
-      </c>
-      <c r="U262" t="n">
-        <v>0</v>
-      </c>
-      <c r="V262" t="n">
-        <v>0</v>
-      </c>
-      <c r="W262" t="n">
-        <v>0</v>
-      </c>
-      <c r="X262" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y262" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE262" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF262" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,22 +53943,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54582,13 +54582,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q275" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AE275" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF275" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG275" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q277" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF277" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G285" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.91</v>
+        <v>7.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.12</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>3.62</v>
+        <v>1.32</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>7.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.6</v>
+        <v>4.12</v>
       </c>
       <c r="R54" t="n">
-        <v>1.32</v>
+        <v>3.62</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.1</v>
+        <v>4.11</v>
       </c>
       <c r="R63" t="n">
-        <v>13</v>
+        <v>5.18</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="R72" t="n">
-        <v>4.09</v>
+        <v>2.4</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14839,10 +14839,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.26</v>
+        <v>1.82</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>12.6</v>
+        <v>3.65</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.82</v>
+        <v>2.57</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="R77" t="n">
-        <v>3.65</v>
+        <v>3.14</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R92" t="n">
-        <v>1.8</v>
+        <v>5.86</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.04</v>
+        <v>7.65</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="R97" t="n">
-        <v>2.53</v>
+        <v>1.48</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.85</v>
+        <v>3.04</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.08</v>
+        <v>3.44</v>
       </c>
       <c r="R101" t="n">
-        <v>3.89</v>
+        <v>2.53</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.96</v>
+        <v>3.6</v>
       </c>
       <c r="R113" t="n">
-        <v>8.25</v>
+        <v>3.1</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="Q168" t="n">
-        <v>2.92</v>
+        <v>3.76</v>
       </c>
       <c r="R168" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.76</v>
+        <v>2.7</v>
       </c>
       <c r="R170" t="n">
-        <v>2.66</v>
+        <v>3.86</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF179" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF189" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q199" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39655,10 +39655,10 @@
         <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF199" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="Q205" t="n">
-        <v>9.199999999999999</v>
+        <v>4.86</v>
       </c>
       <c r="R205" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="R208" t="n">
-        <v>2.66</v>
+        <v>4.47</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>10.1</v>
+        <v>6.29</v>
       </c>
       <c r="Q210" t="n">
-        <v>5.35</v>
+        <v>3.92</v>
       </c>
       <c r="R210" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>6.29</v>
+        <v>2.6</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.92</v>
+        <v>3.14</v>
       </c>
       <c r="R212" t="n">
-        <v>1.53</v>
+        <v>2.66</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF213" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF241" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51278,10 +51278,10 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF258" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,22 +53943,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54582,13 +54582,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q275" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AE275" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF275" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG275" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF277" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q281" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55809,10 +55809,10 @@
         <v>0</v>
       </c>
       <c r="AE281" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF281" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG281" t="n">
         <v>0</v>
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q282" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56006,10 +56006,10 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF282" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG282" t="n">
         <v>0</v>
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -57489,22 +57489,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,22 +57686,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G291" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.38</v>
+        <v>7.55</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.8</v>
+        <v>5.15</v>
       </c>
       <c r="R68" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R69" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>7.55</v>
+        <v>2.85</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.15</v>
+        <v>3.5</v>
       </c>
       <c r="R70" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="R74" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH216" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q236" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -46944,10 +46944,10 @@
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF236" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG236" t="n">
         <v>0</v>
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF242" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54239,10 +54239,10 @@
         <v>0</v>
       </c>
       <c r="AG273" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH273" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI273" t="n">
         <v>0</v>
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q284" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56406,10 +56406,10 @@
         <v>0</v>
       </c>
       <c r="AG284" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH284" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI284" t="n">
         <v>0</v>

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>34</v>
+        <v>1.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>1.02</v>
+        <v>3.62</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12672,10 +12672,10 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>7.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="R68" t="n">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R69" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.85</v>
+        <v>7.55</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.5</v>
+        <v>5.15</v>
       </c>
       <c r="R70" t="n">
-        <v>2.36</v>
+        <v>1.35</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.82</v>
+        <v>2.57</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="R73" t="n">
-        <v>3.65</v>
+        <v>3.14</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.2</v>
+        <v>3.87</v>
       </c>
       <c r="R92" t="n">
-        <v>5.86</v>
+        <v>4.22</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.87</v>
+        <v>3.44</v>
       </c>
       <c r="R93" t="n">
-        <v>4.22</v>
+        <v>2.53</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.04</v>
+        <v>2</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="R101" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="R121" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R122" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="R165" t="n">
-        <v>2.68</v>
+        <v>3.86</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="Q170" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="R170" t="n">
-        <v>3.86</v>
+        <v>2.68</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="R171" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>8.199999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.73</v>
+        <v>3.73</v>
       </c>
       <c r="R172" t="n">
-        <v>1.32</v>
+        <v>2.86</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34336,10 +34336,10 @@
         <v>0</v>
       </c>
       <c r="AE172" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF172" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>6.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q173" t="n">
-        <v>4.72</v>
+        <v>5.73</v>
       </c>
       <c r="R173" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF173" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q176" t="n">
-        <v>4.53</v>
+        <v>2.84</v>
       </c>
       <c r="R176" t="n">
-        <v>5.9</v>
+        <v>3.23</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35469,7 +35469,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF179" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF189" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,55 +38231,55 @@
         </is>
       </c>
       <c r="P192" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R192" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" t="n">
+        <v>0</v>
+      </c>
+      <c r="X192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q192" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R192" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S192" t="n">
-        <v>0</v>
-      </c>
-      <c r="T192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="n">
-        <v>0</v>
-      </c>
-      <c r="V192" t="n">
-        <v>0</v>
-      </c>
-      <c r="W192" t="n">
-        <v>0</v>
-      </c>
-      <c r="X192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE192" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AF192" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.19</v>
+        <v>3.8</v>
       </c>
       <c r="R193" t="n">
-        <v>4.62</v>
+        <v>3.8</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AF193" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39852,10 +39852,10 @@
         <v>0</v>
       </c>
       <c r="AE200" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF200" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG200" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="Q205" t="n">
-        <v>4.86</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R205" t="n">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q206" t="n">
-        <v>9.199999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="R206" t="n">
-        <v>22</v>
+        <v>2.66</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q207" t="n">
-        <v>6.2</v>
+        <v>3.52</v>
       </c>
       <c r="R207" t="n">
-        <v>11.5</v>
+        <v>4.47</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1.79</v>
+        <v>10.1</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.52</v>
+        <v>5.35</v>
       </c>
       <c r="R208" t="n">
-        <v>4.47</v>
+        <v>1.28</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="Q211" t="n">
-        <v>4.21</v>
+        <v>6.2</v>
       </c>
       <c r="R211" t="n">
-        <v>4.83</v>
+        <v>11.5</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.14</v>
+        <v>4.21</v>
       </c>
       <c r="R212" t="n">
-        <v>2.66</v>
+        <v>4.83</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42616,10 +42616,10 @@
         <v>0</v>
       </c>
       <c r="AG214" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH214" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42807,10 +42807,10 @@
         <v>0</v>
       </c>
       <c r="AE215" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF215" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG215" t="n">
         <v>0</v>
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH216" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q223" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,10 +45762,10 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF230" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,22 +46063,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -46944,10 +46944,10 @@
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF236" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG236" t="n">
         <v>0</v>
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q240" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF242" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q244" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF244" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48821,22 +48821,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50490,10 +50490,10 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF254" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="Q258" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
       <c r="R258" t="n">
-        <v>3.1</v>
+        <v>1.79</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51278,10 +51278,10 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF258" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG258" t="n">
         <v>0</v>
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,55 +51824,55 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>3.4</v>
+        <v>5.26</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R261" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="n">
+        <v>0</v>
+      </c>
+      <c r="V261" t="n">
+        <v>0</v>
+      </c>
+      <c r="W261" t="n">
+        <v>0</v>
+      </c>
+      <c r="X261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF261" t="n">
         <v>2.05</v>
-      </c>
-      <c r="S261" t="n">
-        <v>0</v>
-      </c>
-      <c r="T261" t="n">
-        <v>0</v>
-      </c>
-      <c r="U261" t="n">
-        <v>0</v>
-      </c>
-      <c r="V261" t="n">
-        <v>0</v>
-      </c>
-      <c r="W261" t="n">
-        <v>0</v>
-      </c>
-      <c r="X261" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y261" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD261" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE261" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF261" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>5.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q262" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R262" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52066,10 +52066,10 @@
         <v>0</v>
       </c>
       <c r="AE262" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF262" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q263" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54385,13 +54385,13 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q274" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R274" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S274" t="n">
         <v>0</v>
@@ -54430,10 +54430,10 @@
         <v>0</v>
       </c>
       <c r="AE274" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF274" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG274" t="n">
         <v>0</v>
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54582,13 +54582,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q275" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AE275" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF275" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG275" t="n">
         <v>0</v>
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q276" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54824,10 +54824,10 @@
         <v>0</v>
       </c>
       <c r="AE276" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF276" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG276" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q277" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF277" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56406,10 +56406,10 @@
         <v>0</v>
       </c>
       <c r="AG284" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH284" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56603,10 +56603,10 @@
         <v>0</v>
       </c>
       <c r="AG285" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH285" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI285" t="n">
         <v>0</v>
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,22 +57489,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G291" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.91</v>
+        <v>34</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>15</v>
       </c>
       <c r="R52" t="n">
-        <v>3.62</v>
+        <v>1.02</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>34</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="R53" t="n">
-        <v>1.02</v>
+        <v>4.39</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.72</v>
+        <v>2.82</v>
       </c>
       <c r="R56" t="n">
-        <v>10.7</v>
+        <v>2.53</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.38</v>
+        <v>7.55</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.8</v>
+        <v>5.15</v>
       </c>
       <c r="R68" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R69" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>7.55</v>
+        <v>2.85</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.15</v>
+        <v>3.5</v>
       </c>
       <c r="R70" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="Q79" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="R79" t="n">
-        <v>12.6</v>
+        <v>4.09</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R81" t="n">
-        <v>4.09</v>
+        <v>3.65</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17597,10 +17597,10 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,14 +18137,14 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R90" t="n">
         <v>3.2</v>
       </c>
-      <c r="R90" t="n">
-        <v>5.86</v>
-      </c>
       <c r="S90" t="n">
         <v>0</v>
       </c>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R93" t="n">
-        <v>2.53</v>
+        <v>1.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.21</v>
+        <v>1.85</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.27</v>
+        <v>4.08</v>
       </c>
       <c r="R104" t="n">
-        <v>2.26</v>
+        <v>3.89</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.8</v>
+        <v>7.65</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R105" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>3.89</v>
+        <v>2.44</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q132" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R132" t="n">
-        <v>2.6</v>
+        <v>3.43</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.7</v>
+        <v>4.01</v>
       </c>
       <c r="R165" t="n">
-        <v>3.86</v>
+        <v>4.37</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="R166" t="n">
-        <v>3.59</v>
+        <v>2.68</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q170" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="R170" t="n">
-        <v>2.68</v>
+        <v>3.86</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="Q176" t="n">
-        <v>2.84</v>
+        <v>3.28</v>
       </c>
       <c r="R176" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF176" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35469,7 +35469,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35666,17 +35666,17 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF179" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q180" t="n">
-        <v>4.53</v>
+        <v>2.84</v>
       </c>
       <c r="R180" t="n">
-        <v>5.9</v>
+        <v>3.23</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35912,10 +35912,10 @@
         <v>0</v>
       </c>
       <c r="AE180" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF180" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="R188" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="R192" t="n">
-        <v>4.62</v>
+        <v>3.61</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q194" t="n">
-        <v>5.43</v>
+        <v>3.19</v>
       </c>
       <c r="R194" t="n">
-        <v>8.800000000000001</v>
+        <v>4.62</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AF194" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>7.46</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39464,10 +39464,10 @@
         <v>0</v>
       </c>
       <c r="AG198" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH198" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39852,10 +39852,10 @@
         <v>0</v>
       </c>
       <c r="AE200" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF200" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG200" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="Q205" t="n">
-        <v>9.199999999999999</v>
+        <v>4.21</v>
       </c>
       <c r="R205" t="n">
-        <v>22</v>
+        <v>4.83</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.79</v>
+        <v>6.29</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="R207" t="n">
-        <v>4.47</v>
+        <v>1.53</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>10.1</v>
+        <v>1.22</v>
       </c>
       <c r="Q208" t="n">
-        <v>5.35</v>
+        <v>6.2</v>
       </c>
       <c r="R208" t="n">
-        <v>1.28</v>
+        <v>11.5</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Q211" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R211" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="Q212" t="n">
-        <v>4.21</v>
+        <v>3.38</v>
       </c>
       <c r="R212" t="n">
-        <v>4.83</v>
+        <v>3.83</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.7</v>
+        <v>4.86</v>
       </c>
       <c r="R214" t="n">
-        <v>3.02</v>
+        <v>9.4</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42610,16 +42610,16 @@
         <v>0</v>
       </c>
       <c r="AE214" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF214" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG214" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH214" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42807,10 +42807,10 @@
         <v>0</v>
       </c>
       <c r="AE215" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF215" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG215" t="n">
         <v>0</v>
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH216" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43595,10 +43595,10 @@
         <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF219" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG219" t="n">
         <v>0</v>
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,10 +43792,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF220" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q221" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43995,10 +43995,10 @@
         <v>0</v>
       </c>
       <c r="AG221" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH221" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI221" t="n">
         <v>0</v>
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q222" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF222" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="R223" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF223" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44777,10 +44777,10 @@
         <v>0</v>
       </c>
       <c r="AE225" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF225" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>2.28</v>
+        <v>10.6</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.25</v>
+        <v>6.02</v>
       </c>
       <c r="R230" t="n">
-        <v>3.06</v>
+        <v>1.3</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,10 +45762,10 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF230" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45959,10 +45959,10 @@
         <v>0</v>
       </c>
       <c r="AE231" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF231" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
@@ -46063,22 +46063,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q232" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46156,10 +46156,10 @@
         <v>0</v>
       </c>
       <c r="AE232" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF232" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG232" t="n">
         <v>0</v>
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>3.94</v>
+        <v>2.22</v>
       </c>
       <c r="Q241" t="n">
-        <v>4.11</v>
+        <v>3.1</v>
       </c>
       <c r="R241" t="n">
-        <v>1.93</v>
+        <v>3.32</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF242" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48230,22 +48230,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF243" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF253" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50687,10 +50687,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF255" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>2.05</v>
+        <v>3.24</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="R256" t="n">
-        <v>3.69</v>
+        <v>2.26</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50884,10 +50884,10 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF256" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG256" t="n">
         <v>0</v>
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF257" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q260" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q263" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52809,13 +52809,13 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q266" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S266" t="n">
         <v>0</v>
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q271" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54385,13 +54385,13 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q274" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S274" t="n">
         <v>0</v>
@@ -54430,10 +54430,10 @@
         <v>0</v>
       </c>
       <c r="AE274" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF274" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG274" t="n">
         <v>0</v>
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54582,13 +54582,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q275" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R275" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AE275" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AF275" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG275" t="n">
         <v>0</v>
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q276" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54824,10 +54824,10 @@
         <v>0</v>
       </c>
       <c r="AE276" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF276" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG276" t="n">
         <v>0</v>
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q278" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55218,10 +55218,10 @@
         <v>0</v>
       </c>
       <c r="AE278" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF278" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG278" t="n">
         <v>0</v>
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q279" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55415,10 +55415,10 @@
         <v>0</v>
       </c>
       <c r="AE279" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF279" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG279" t="n">
         <v>0</v>
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q281" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55809,10 +55809,10 @@
         <v>0</v>
       </c>
       <c r="AE281" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF281" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG281" t="n">
         <v>0</v>
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q282" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R282" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56012,10 +56012,10 @@
         <v>0</v>
       </c>
       <c r="AG282" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH282" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF283" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q284" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF284" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q285" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56603,10 +56603,10 @@
         <v>0</v>
       </c>
       <c r="AG285" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH285" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI285" t="n">
         <v>0</v>
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q287" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -56991,10 +56991,10 @@
         <v>0</v>
       </c>
       <c r="AE287" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF287" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG287" t="n">
         <v>0</v>
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,22 +57686,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G291" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>7.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.6</v>
+        <v>4.12</v>
       </c>
       <c r="R51" t="n">
-        <v>1.32</v>
+        <v>3.62</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="R53" t="n">
-        <v>4.39</v>
+        <v>1.32</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12672,10 +12672,10 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>2.65</v>
+        <v>3.29</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R70" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R71" t="n">
-        <v>3.29</v>
+        <v>2.36</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="R72" t="n">
-        <v>3.02</v>
+        <v>4.09</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14839,10 +14839,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="R79" t="n">
-        <v>4.09</v>
+        <v>12.6</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="R87" t="n">
-        <v>1.68</v>
+        <v>3.02</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17597,10 +17597,10 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.48</v>
+        <v>3.87</v>
       </c>
       <c r="R90" t="n">
-        <v>3.2</v>
+        <v>4.22</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.9</v>
+        <v>4.08</v>
       </c>
       <c r="R93" t="n">
-        <v>1.8</v>
+        <v>3.89</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R94" t="n">
-        <v>2.53</v>
+        <v>1.8</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.21</v>
+        <v>1.69</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="R97" t="n">
-        <v>2.26</v>
+        <v>5.86</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.08</v>
+        <v>4.96</v>
       </c>
       <c r="R112" t="n">
-        <v>2.99</v>
+        <v>8.25</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R113" t="n">
-        <v>3.1</v>
+        <v>3.89</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF113" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q115" t="n">
-        <v>4.96</v>
+        <v>3.08</v>
       </c>
       <c r="R115" t="n">
-        <v>8.25</v>
+        <v>2.99</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R121" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="R122" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q132" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R132" t="n">
-        <v>3.43</v>
+        <v>2.6</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="R162" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R163" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="Q165" t="n">
-        <v>4.01</v>
+        <v>2.7</v>
       </c>
       <c r="R165" t="n">
-        <v>4.37</v>
+        <v>3.86</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q166" t="n">
-        <v>2.92</v>
+        <v>4.01</v>
       </c>
       <c r="R166" t="n">
-        <v>2.68</v>
+        <v>4.37</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.76</v>
+        <v>3.28</v>
       </c>
       <c r="R168" t="n">
-        <v>2.66</v>
+        <v>3.59</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="Q170" t="n">
-        <v>2.7</v>
+        <v>3.74</v>
       </c>
       <c r="R170" t="n">
-        <v>3.86</v>
+        <v>3.51</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="R171" t="n">
-        <v>3.51</v>
+        <v>2.68</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.28</v>
+        <v>2.84</v>
       </c>
       <c r="R176" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35469,7 +35469,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.52</v>
+        <v>2.09</v>
       </c>
       <c r="Q180" t="n">
-        <v>2.84</v>
+        <v>4.15</v>
       </c>
       <c r="R180" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35912,10 +35912,10 @@
         <v>0</v>
       </c>
       <c r="AE180" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF180" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG180" t="n">
         <v>0</v>
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q181" t="n">
-        <v>4.53</v>
+        <v>3.28</v>
       </c>
       <c r="R181" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.82</v>
+        <v>2.04</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.11</v>
+        <v>3.54</v>
       </c>
       <c r="R182" t="n">
-        <v>2.51</v>
+        <v>3.65</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF182" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="R192" t="n">
-        <v>3.61</v>
+        <v>4.62</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF192" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="R194" t="n">
-        <v>4.62</v>
+        <v>3.61</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF197" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40049,10 +40049,10 @@
         <v>0</v>
       </c>
       <c r="AE201" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF201" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG201" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q204" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="Q205" t="n">
-        <v>4.21</v>
+        <v>6.2</v>
       </c>
       <c r="R205" t="n">
-        <v>4.83</v>
+        <v>11.5</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>2.6</v>
+        <v>1.09</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R206" t="n">
-        <v>2.66</v>
+        <v>22</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>6.29</v>
+        <v>10.1</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.92</v>
+        <v>5.35</v>
       </c>
       <c r="R207" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41335,22 +41335,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="Q208" t="n">
-        <v>6.2</v>
+        <v>4.21</v>
       </c>
       <c r="R208" t="n">
-        <v>11.5</v>
+        <v>4.83</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF208" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>10.1</v>
+        <v>1.79</v>
       </c>
       <c r="Q209" t="n">
-        <v>5.35</v>
+        <v>3.52</v>
       </c>
       <c r="R209" t="n">
-        <v>1.28</v>
+        <v>4.47</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.09</v>
+        <v>1.96</v>
       </c>
       <c r="Q211" t="n">
-        <v>9.199999999999999</v>
+        <v>3.38</v>
       </c>
       <c r="R211" t="n">
-        <v>22</v>
+        <v>3.83</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42610,10 +42610,10 @@
         <v>0</v>
       </c>
       <c r="AE214" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF214" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG214" t="n">
         <v>0</v>
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42813,10 +42813,10 @@
         <v>0</v>
       </c>
       <c r="AG215" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH215" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI215" t="n">
         <v>0</v>
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.7</v>
+        <v>4.86</v>
       </c>
       <c r="R216" t="n">
-        <v>3.02</v>
+        <v>9.4</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43004,16 +43004,16 @@
         <v>0</v>
       </c>
       <c r="AE216" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF216" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG216" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH216" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>3.44</v>
+        <v>2.69</v>
       </c>
       <c r="Q219" t="n">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="R219" t="n">
-        <v>2.09</v>
+        <v>2.67</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43595,10 +43595,10 @@
         <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AF219" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG219" t="n">
         <v>0</v>
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1.89</v>
+        <v>3.42</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.83</v>
+        <v>3.56</v>
       </c>
       <c r="R220" t="n">
-        <v>3.91</v>
+        <v>2.11</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,10 +43792,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AF220" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>1.31</v>
+        <v>2.99</v>
       </c>
       <c r="Q221" t="n">
-        <v>5.98</v>
+        <v>3.46</v>
       </c>
       <c r="R221" t="n">
-        <v>8.65</v>
+        <v>2.36</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43989,16 +43989,16 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF221" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG221" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH221" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44144,10 +44144,10 @@
         <v>3.42</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="R222" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF222" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>2.99</v>
+        <v>1.31</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.46</v>
+        <v>5.98</v>
       </c>
       <c r="R223" t="n">
-        <v>2.36</v>
+        <v>8.65</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,16 +44383,16 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF223" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG223" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH223" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI223" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="R224" t="n">
-        <v>3.89</v>
+        <v>2.93</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>2.69</v>
+        <v>2.03</v>
       </c>
       <c r="Q225" t="n">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="R225" t="n">
-        <v>2.67</v>
+        <v>3.64</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44777,10 +44777,10 @@
         <v>0</v>
       </c>
       <c r="AE225" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AF225" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AG225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q226" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF226" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q227" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF227" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q228" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.59</v>
+        <v>3.21</v>
       </c>
       <c r="R229" t="n">
-        <v>3.64</v>
+        <v>3.89</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF229" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="Q231" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45959,10 +45959,10 @@
         <v>0</v>
       </c>
       <c r="AE231" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF231" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
@@ -46063,22 +46063,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q232" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46156,10 +46156,10 @@
         <v>0</v>
       </c>
       <c r="AE232" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF232" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG232" t="n">
         <v>0</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -46747,10 +46747,10 @@
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF235" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG235" t="n">
         <v>0</v>
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47141,10 +47141,10 @@
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF237" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG237" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF242" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q244" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF244" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -48914,10 +48914,10 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF246" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49111,10 +49111,10 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF247" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG247" t="n">
         <v>0</v>
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF249" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.38</v>
+        <v>3.86</v>
       </c>
       <c r="R253" t="n">
-        <v>3.45</v>
+        <v>4.29</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF253" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AF253" t="n">
-        <v>1.8</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="Q254" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
       <c r="R254" t="n">
-        <v>3.1</v>
+        <v>1.79</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50490,10 +50490,10 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF254" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q255" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50687,10 +50687,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF255" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50884,10 +50884,10 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF256" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Q257" t="n">
-        <v>3.38</v>
+        <v>2.85</v>
       </c>
       <c r="R257" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AF257" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="R258" t="n">
-        <v>1.79</v>
+        <v>3.69</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>5.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q261" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R261" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -51869,10 +51869,10 @@
         <v>0</v>
       </c>
       <c r="AE261" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF261" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,55 +52021,55 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>3.4</v>
+        <v>5.26</v>
       </c>
       <c r="Q262" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R262" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="n">
+        <v>0</v>
+      </c>
+      <c r="V262" t="n">
+        <v>0</v>
+      </c>
+      <c r="W262" t="n">
+        <v>0</v>
+      </c>
+      <c r="X262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF262" t="n">
         <v>2.05</v>
-      </c>
-      <c r="S262" t="n">
-        <v>0</v>
-      </c>
-      <c r="T262" t="n">
-        <v>0</v>
-      </c>
-      <c r="U262" t="n">
-        <v>0</v>
-      </c>
-      <c r="V262" t="n">
-        <v>0</v>
-      </c>
-      <c r="W262" t="n">
-        <v>0</v>
-      </c>
-      <c r="X262" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y262" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD262" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE262" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF262" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q276" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54824,10 +54824,10 @@
         <v>0</v>
       </c>
       <c r="AE276" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF276" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG276" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF277" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q282" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56012,10 +56012,10 @@
         <v>0</v>
       </c>
       <c r="AG282" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH282" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56603,10 +56603,10 @@
         <v>0</v>
       </c>
       <c r="AG285" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH285" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI285" t="n">
         <v>0</v>
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q287" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -56991,10 +56991,10 @@
         <v>0</v>
       </c>
       <c r="AE287" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF287" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG287" t="n">
         <v>0</v>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57143,13 +57143,13 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q288" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R288" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S288" t="n">
         <v>0</v>
@@ -57188,10 +57188,10 @@
         <v>0</v>
       </c>
       <c r="AE288" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF288" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG288" t="n">
         <v>0</v>
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.91</v>
+        <v>7.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.12</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>3.62</v>
+        <v>1.32</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>7.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.6</v>
+        <v>4.12</v>
       </c>
       <c r="R53" t="n">
-        <v>1.32</v>
+        <v>3.62</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.82</v>
+        <v>5.72</v>
       </c>
       <c r="R59" t="n">
-        <v>2.53</v>
+        <v>10.7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.32</v>
+        <v>2.82</v>
       </c>
       <c r="R60" t="n">
-        <v>3.21</v>
+        <v>2.53</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R69" t="n">
-        <v>3.29</v>
+        <v>2.36</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>2.36</v>
+        <v>3.29</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14839,10 +14839,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="R78" t="n">
-        <v>3.14</v>
+        <v>4.09</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.26</v>
+        <v>2.57</v>
       </c>
       <c r="Q79" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="R79" t="n">
-        <v>12.6</v>
+        <v>3.14</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="Q80" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="R80" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="R89" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>7.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R95" t="n">
-        <v>1.48</v>
+        <v>5.86</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.69</v>
+        <v>3.21</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="R97" t="n">
-        <v>5.86</v>
+        <v>2.26</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.48</v>
+        <v>4.08</v>
       </c>
       <c r="R101" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="R102" t="n">
-        <v>3.64</v>
+        <v>4.22</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.21</v>
+        <v>7.65</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="R103" t="n">
-        <v>2.26</v>
+        <v>1.48</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="R108" t="n">
-        <v>2.44</v>
+        <v>3.89</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.35</v>
+        <v>4.96</v>
       </c>
       <c r="R109" t="n">
-        <v>2.65</v>
+        <v>8.25</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.44</v>
+        <v>2.47</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.96</v>
+        <v>3.35</v>
       </c>
       <c r="R112" t="n">
-        <v>8.25</v>
+        <v>2.65</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>3.89</v>
+        <v>2.44</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R162" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q164" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="R165" t="n">
-        <v>3.86</v>
+        <v>3.59</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="R168" t="n">
-        <v>3.59</v>
+        <v>2.68</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="R169" t="n">
-        <v>2.66</v>
+        <v>3.51</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q171" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="R171" t="n">
-        <v>2.68</v>
+        <v>3.86</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.73</v>
+        <v>5.73</v>
       </c>
       <c r="R172" t="n">
-        <v>2.86</v>
+        <v>1.32</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34336,10 +34336,10 @@
         <v>0</v>
       </c>
       <c r="AE172" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF172" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG172" t="n">
         <v>0</v>
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>8.199999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="Q173" t="n">
-        <v>5.73</v>
+        <v>3.73</v>
       </c>
       <c r="R173" t="n">
-        <v>1.32</v>
+        <v>2.86</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF173" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6.62</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="R52" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AF52" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.45</v>
+        <v>4.12</v>
       </c>
       <c r="R54" t="n">
-        <v>4.39</v>
+        <v>3.62</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.12</v>
+        <v>3.45</v>
       </c>
       <c r="R56" t="n">
-        <v>3.62</v>
+        <v>4.39</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="R59" t="n">
-        <v>2.53</v>
+        <v>3.21</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.38</v>
+        <v>7.55</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>5.15</v>
       </c>
       <c r="R71" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.11</v>
+        <v>3.8</v>
       </c>
       <c r="R73" t="n">
-        <v>4.59</v>
+        <v>4.09</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.82</v>
+        <v>1.26</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R76" t="n">
-        <v>3.65</v>
+        <v>12.6</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.8</v>
+        <v>3.11</v>
       </c>
       <c r="R78" t="n">
-        <v>4.09</v>
+        <v>4.59</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.74</v>
+        <v>2.52</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="R89" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="R93" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.08</v>
+        <v>3.87</v>
       </c>
       <c r="R94" t="n">
-        <v>3.89</v>
+        <v>4.22</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="R97" t="n">
-        <v>3.64</v>
+        <v>2.53</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="R99" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="R100" t="n">
-        <v>4.22</v>
+        <v>5.86</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R110" t="n">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="R118" t="n">
-        <v>3.7</v>
+        <v>2.99</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="R123" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R124" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R165" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q168" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="R168" t="n">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="R170" t="n">
-        <v>3.59</v>
+        <v>3.86</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.76</v>
+        <v>2.92</v>
       </c>
       <c r="R171" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q173" t="n">
-        <v>2.7</v>
+        <v>3.76</v>
       </c>
       <c r="R173" t="n">
-        <v>3.86</v>
+        <v>2.66</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35469,17 +35469,17 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35518,10 +35518,10 @@
         <v>0</v>
       </c>
       <c r="AE178" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF178" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="Q179" t="n">
-        <v>4.53</v>
+        <v>3.54</v>
       </c>
       <c r="R179" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF179" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37833,17 +37833,17 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF190" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R193" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.39</v>
+        <v>2.03</v>
       </c>
       <c r="Q194" t="n">
-        <v>5.43</v>
+        <v>3.3</v>
       </c>
       <c r="R194" t="n">
-        <v>8.800000000000001</v>
+        <v>3.61</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.8</v>
+        <v>5.43</v>
       </c>
       <c r="R196" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AF196" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>7.46</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39267,10 +39267,10 @@
         <v>0</v>
       </c>
       <c r="AG197" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH197" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI197" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>7.46</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39858,10 +39858,10 @@
         <v>0</v>
       </c>
       <c r="AG200" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH200" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI200" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>10.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q206" t="n">
-        <v>5.35</v>
+        <v>3.38</v>
       </c>
       <c r="R206" t="n">
-        <v>1.28</v>
+        <v>3.83</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.96</v>
+        <v>1.42</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.38</v>
+        <v>4.86</v>
       </c>
       <c r="R207" t="n">
-        <v>3.83</v>
+        <v>9.4</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Q208" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R208" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q210" t="n">
-        <v>9.199999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="R210" t="n">
-        <v>22</v>
+        <v>2.66</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>6.29</v>
+        <v>1.79</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="R211" t="n">
-        <v>1.53</v>
+        <v>4.47</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.79</v>
+        <v>10.1</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.52</v>
+        <v>5.35</v>
       </c>
       <c r="R212" t="n">
-        <v>4.47</v>
+        <v>1.28</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.6</v>
+        <v>1.22</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.14</v>
+        <v>6.2</v>
       </c>
       <c r="R213" t="n">
-        <v>2.66</v>
+        <v>11.5</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42610,10 +42610,10 @@
         <v>0</v>
       </c>
       <c r="AE214" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF214" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG214" t="n">
         <v>0</v>
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42807,10 +42807,10 @@
         <v>0</v>
       </c>
       <c r="AE215" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF215" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG215" t="n">
         <v>0</v>
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH216" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43207,10 +43207,10 @@
         <v>0</v>
       </c>
       <c r="AG217" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH217" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI217" t="n">
         <v>0</v>
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF218" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R220" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43792,10 +43792,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF220" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>2.11</v>
+        <v>3.44</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="R221" t="n">
-        <v>3.89</v>
+        <v>2.09</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43989,10 +43989,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF221" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF223" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44777,10 +44777,10 @@
         <v>0</v>
       </c>
       <c r="AE225" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG225" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="R226" t="n">
-        <v>2.11</v>
+        <v>2.93</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AF226" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45368,10 +45368,10 @@
         <v>0</v>
       </c>
       <c r="AE228" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF228" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG228" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45720,10 +45720,10 @@
         <v>3.42</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="R230" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,10 +45762,10 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF230" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -46063,22 +46063,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q232" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46353,10 +46353,10 @@
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF233" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG233" t="n">
         <v>0</v>
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>2.28</v>
+        <v>6.49</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="R238" t="n">
-        <v>3.06</v>
+        <v>1.5</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47338,10 +47338,10 @@
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF238" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AG238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47732,10 +47732,10 @@
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF240" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG240" t="n">
         <v>0</v>
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>5.64</v>
+        <v>1.15</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.98</v>
+        <v>7.85</v>
       </c>
       <c r="R241" t="n">
-        <v>1.49</v>
+        <v>10.5</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>1.15</v>
+        <v>5.64</v>
       </c>
       <c r="Q242" t="n">
-        <v>7.85</v>
+        <v>3.98</v>
       </c>
       <c r="R242" t="n">
-        <v>10.5</v>
+        <v>1.49</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF243" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>3.94</v>
+        <v>3.23</v>
       </c>
       <c r="Q244" t="n">
-        <v>4.11</v>
+        <v>3.6</v>
       </c>
       <c r="R244" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AF244" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48821,22 +48821,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -48914,10 +48914,10 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF246" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="Q248" t="n">
-        <v>3.18</v>
+        <v>3.86</v>
       </c>
       <c r="R248" t="n">
-        <v>3.69</v>
+        <v>4.29</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Q250" t="n">
-        <v>3.38</v>
+        <v>2.85</v>
       </c>
       <c r="R250" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AF250" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q252" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF252" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50293,10 +50293,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF253" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50490,10 +50490,10 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF254" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="Q255" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="R255" t="n">
-        <v>4.29</v>
+        <v>3.56</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50687,10 +50687,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AF255" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50884,10 +50884,10 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF256" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF257" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,22 +51776,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52809,13 +52809,13 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q266" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S266" t="n">
         <v>0</v>
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,13 +53006,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q267" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53597,13 +53597,13 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q270" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R270" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q271" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF277" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q279" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55415,10 +55415,10 @@
         <v>0</v>
       </c>
       <c r="AE279" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF279" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG279" t="n">
         <v>0</v>
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55567,13 +55567,13 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q280" t="n">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="R280" t="n">
-        <v>2.67</v>
+        <v>5.19</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -55612,10 +55612,10 @@
         <v>0</v>
       </c>
       <c r="AE280" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF280" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG280" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="Q281" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="R281" t="n">
-        <v>5.19</v>
+        <v>2.67</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55809,10 +55809,10 @@
         <v>0</v>
       </c>
       <c r="AE281" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF281" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG281" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>3.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R284" t="n">
-        <v>2.05</v>
+        <v>6.25</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1.65</v>
+        <v>3.24</v>
       </c>
       <c r="Q285" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R285" t="n">
-        <v>5.15</v>
+        <v>2.05</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,16 +56597,16 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF285" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG285" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH285" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI285" t="n">
         <v>0</v>
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q286" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56800,10 +56800,10 @@
         <v>0</v>
       </c>
       <c r="AG286" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH286" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI286" t="n">
         <v>0</v>
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,22 +57883,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58080,22 +58080,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G293" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>6.62</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>7.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.6</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>1.32</v>
+        <v>3.62</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>34</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="R53" t="n">
-        <v>1.02</v>
+        <v>4.39</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.91</v>
+        <v>7.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.12</v>
+        <v>4.6</v>
       </c>
       <c r="R54" t="n">
-        <v>3.62</v>
+        <v>1.32</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.82</v>
+        <v>5.72</v>
       </c>
       <c r="R60" t="n">
-        <v>2.53</v>
+        <v>10.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.38</v>
+        <v>7.55</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.8</v>
+        <v>5.15</v>
       </c>
       <c r="R70" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>7.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R72" t="n">
-        <v>3.29</v>
+        <v>2.36</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="R73" t="n">
-        <v>4.09</v>
+        <v>2.4</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="R74" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.78</v>
+        <v>3.11</v>
       </c>
       <c r="R75" t="n">
-        <v>3.84</v>
+        <v>4.59</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.57</v>
+        <v>1.82</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="R81" t="n">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.2</v>
+        <v>1.76</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R82" t="n">
-        <v>1.68</v>
+        <v>4.09</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="R84" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17006,10 +17006,10 @@
         <v>0</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="R85" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="R93" t="n">
-        <v>1.8</v>
+        <v>4.22</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.87</v>
+        <v>3.44</v>
       </c>
       <c r="R94" t="n">
-        <v>4.22</v>
+        <v>2.53</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>7.65</v>
+        <v>1.91</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="R101" t="n">
-        <v>1.48</v>
+        <v>3.64</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R115" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.35</v>
+        <v>4.96</v>
       </c>
       <c r="R116" t="n">
-        <v>2.65</v>
+        <v>8.25</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="R118" t="n">
-        <v>2.99</v>
+        <v>3.7</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="R120" t="n">
-        <v>3.89</v>
+        <v>2.65</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R123" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="R124" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="R165" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R166" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="Q167" t="n">
-        <v>4.01</v>
+        <v>3.28</v>
       </c>
       <c r="R167" t="n">
-        <v>4.37</v>
+        <v>3.59</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="R168" t="n">
-        <v>3.59</v>
+        <v>3.86</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="R169" t="n">
-        <v>3.51</v>
+        <v>2.68</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q171" t="n">
-        <v>2.92</v>
+        <v>4.01</v>
       </c>
       <c r="R171" t="n">
-        <v>2.68</v>
+        <v>4.37</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF174" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>8.199999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="Q175" t="n">
-        <v>5.73</v>
+        <v>4.72</v>
       </c>
       <c r="R175" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34927,10 +34927,10 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF175" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35469,7 +35469,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF179" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.09</v>
+        <v>2.52</v>
       </c>
       <c r="Q180" t="n">
-        <v>4.15</v>
+        <v>2.84</v>
       </c>
       <c r="R180" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35912,10 +35912,10 @@
         <v>0</v>
       </c>
       <c r="AE180" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF180" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG180" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36257,7 +36257,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF190" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,55 +38428,55 @@
         </is>
       </c>
       <c r="P193" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R193" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" t="n">
+        <v>0</v>
+      </c>
+      <c r="X193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q193" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R193" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S193" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="n">
-        <v>0</v>
-      </c>
-      <c r="V193" t="n">
-        <v>0</v>
-      </c>
-      <c r="W193" t="n">
-        <v>0</v>
-      </c>
-      <c r="X193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE193" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AF193" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R194" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="R195" t="n">
-        <v>4.62</v>
+        <v>3.61</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>7.46</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39267,10 +39267,10 @@
         <v>0</v>
       </c>
       <c r="AG197" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH197" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39458,10 +39458,10 @@
         <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF198" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q199" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39655,10 +39655,10 @@
         <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF199" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>7.46</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39858,10 +39858,10 @@
         <v>0</v>
       </c>
       <c r="AG200" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH200" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI200" t="n">
         <v>0</v>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40049,10 +40049,10 @@
         <v>0</v>
       </c>
       <c r="AE201" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF201" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40246,10 +40246,10 @@
         <v>0</v>
       </c>
       <c r="AE202" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF202" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG202" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>6.29</v>
+        <v>1.71</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.92</v>
+        <v>4.21</v>
       </c>
       <c r="R205" t="n">
-        <v>1.53</v>
+        <v>4.83</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="R206" t="n">
-        <v>3.83</v>
+        <v>3.02</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41040,10 +41040,10 @@
         <v>0</v>
       </c>
       <c r="AG206" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH206" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.42</v>
+        <v>2.6</v>
       </c>
       <c r="Q207" t="n">
-        <v>4.86</v>
+        <v>3.14</v>
       </c>
       <c r="R207" t="n">
-        <v>9.4</v>
+        <v>2.66</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="R210" t="n">
-        <v>2.66</v>
+        <v>4.47</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.79</v>
+        <v>10.1</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.52</v>
+        <v>5.35</v>
       </c>
       <c r="R211" t="n">
-        <v>4.47</v>
+        <v>1.28</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>10.1</v>
+        <v>1.42</v>
       </c>
       <c r="Q212" t="n">
-        <v>5.35</v>
+        <v>4.86</v>
       </c>
       <c r="R212" t="n">
-        <v>1.28</v>
+        <v>9.4</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH216" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.21</v>
+        <v>3.38</v>
       </c>
       <c r="R218" t="n">
-        <v>4.83</v>
+        <v>3.83</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF218" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>3.44</v>
+        <v>2.11</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="R221" t="n">
-        <v>2.09</v>
+        <v>3.89</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43989,10 +43989,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF221" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF222" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q223" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF223" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>1.31</v>
+        <v>3.42</v>
       </c>
       <c r="Q224" t="n">
-        <v>5.98</v>
+        <v>3.1</v>
       </c>
       <c r="R224" t="n">
-        <v>8.65</v>
+        <v>2.17</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44586,10 +44586,10 @@
         <v>0</v>
       </c>
       <c r="AG224" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH224" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI224" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44777,10 +44777,10 @@
         <v>0</v>
       </c>
       <c r="AE225" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF225" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG225" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="R226" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AF226" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>2.99</v>
+        <v>1.89</v>
       </c>
       <c r="Q227" t="n">
-        <v>3.46</v>
+        <v>3.83</v>
       </c>
       <c r="R227" t="n">
-        <v>2.36</v>
+        <v>3.91</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AF227" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>1.89</v>
+        <v>2.99</v>
       </c>
       <c r="Q228" t="n">
-        <v>3.83</v>
+        <v>3.46</v>
       </c>
       <c r="R228" t="n">
-        <v>3.91</v>
+        <v>2.36</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45368,10 +45368,10 @@
         <v>0</v>
       </c>
       <c r="AE228" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AF228" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AG228" t="n">
         <v>0</v>
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="R229" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF229" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>3.42</v>
+        <v>1.31</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.56</v>
+        <v>5.98</v>
       </c>
       <c r="R230" t="n">
-        <v>2.11</v>
+        <v>8.65</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,16 +45762,16 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF230" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG230" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH230" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,14 +45914,14 @@
         </is>
       </c>
       <c r="P231" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="R231" t="n">
         <v>2.11</v>
       </c>
-      <c r="Q231" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="R231" t="n">
-        <v>3.89</v>
-      </c>
       <c r="S231" t="n">
         <v>0</v>
       </c>
@@ -45959,10 +45959,10 @@
         <v>0</v>
       </c>
       <c r="AE231" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF231" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q232" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="Q233" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="R233" t="n">
-        <v>3.06</v>
+        <v>4.24</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46353,10 +46353,10 @@
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF233" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG233" t="n">
         <v>0</v>
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF234" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="Q236" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -46944,10 +46944,10 @@
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF236" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG236" t="n">
         <v>0</v>
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="Q237" t="n">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47338,10 +47338,10 @@
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF238" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG238" t="n">
         <v>0</v>
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48624,22 +48624,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>2.22</v>
+        <v>3.23</v>
       </c>
       <c r="Q245" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R245" t="n">
-        <v>3.32</v>
+        <v>2.26</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF245" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF250" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF252" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q254" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50490,10 +50490,10 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF254" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q255" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="R255" t="n">
-        <v>3.56</v>
+        <v>3.69</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50687,10 +50687,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF255" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF257" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>3.8</v>
+        <v>2.19</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="R258" t="n">
-        <v>1.79</v>
+        <v>3.45</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51278,10 +51278,10 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF258" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51475,10 +51475,10 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF259" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q260" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51672,10 +51672,10 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF260" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q261" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -51869,10 +51869,10 @@
         <v>0</v>
       </c>
       <c r="AE261" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF261" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG261" t="n">
         <v>0</v>
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,55 +52218,55 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>3.4</v>
+        <v>5.26</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R263" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="n">
+        <v>0</v>
+      </c>
+      <c r="V263" t="n">
+        <v>0</v>
+      </c>
+      <c r="W263" t="n">
+        <v>0</v>
+      </c>
+      <c r="X263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF263" t="n">
         <v>2.05</v>
-      </c>
-      <c r="S263" t="n">
-        <v>0</v>
-      </c>
-      <c r="T263" t="n">
-        <v>0</v>
-      </c>
-      <c r="U263" t="n">
-        <v>0</v>
-      </c>
-      <c r="V263" t="n">
-        <v>0</v>
-      </c>
-      <c r="W263" t="n">
-        <v>0</v>
-      </c>
-      <c r="X263" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y263" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE263" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF263" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG263" t="n">
         <v>0</v>
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>5.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q264" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R264" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52460,10 +52460,10 @@
         <v>0</v>
       </c>
       <c r="AE264" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF264" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53006,13 +53006,13 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q267" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,13 +53203,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q268" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53597,13 +53597,13 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q270" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q271" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q277" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF277" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q279" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55415,10 +55415,10 @@
         <v>0</v>
       </c>
       <c r="AE279" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF279" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG279" t="n">
         <v>0</v>
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55567,13 +55567,13 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="Q280" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="R280" t="n">
-        <v>5.19</v>
+        <v>2.67</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -55612,10 +55612,10 @@
         <v>0</v>
       </c>
       <c r="AE280" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF280" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG280" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q281" t="n">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="R281" t="n">
-        <v>2.67</v>
+        <v>5.19</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55809,10 +55809,10 @@
         <v>0</v>
       </c>
       <c r="AE281" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF281" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG281" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1.6</v>
+        <v>3.24</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R284" t="n">
-        <v>6.25</v>
+        <v>2.05</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,10 +56400,10 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>3.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R285" t="n">
-        <v>2.05</v>
+        <v>6.25</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AF285" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -57292,7 +57292,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57340,13 +57340,13 @@
         </is>
       </c>
       <c r="P289" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q289" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R289" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
@@ -57385,10 +57385,10 @@
         <v>0</v>
       </c>
       <c r="AE289" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF289" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG289" t="n">
         <v>0</v>
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57537,13 +57537,13 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q290" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S290" t="n">
         <v>0</v>
@@ -57582,10 +57582,10 @@
         <v>0</v>
       </c>
       <c r="AE290" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF290" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG290" t="n">
         <v>0</v>

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>6.62</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.45</v>
+        <v>4.12</v>
       </c>
       <c r="R53" t="n">
-        <v>4.39</v>
+        <v>3.62</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="R54" t="n">
-        <v>1.32</v>
+        <v>4.39</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.05</v>
+        <v>1.34</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.32</v>
+        <v>5.72</v>
       </c>
       <c r="R61" t="n">
-        <v>3.21</v>
+        <v>10.7</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="R62" t="n">
-        <v>2.53</v>
+        <v>3.21</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.1</v>
+        <v>4.11</v>
       </c>
       <c r="R63" t="n">
-        <v>13</v>
+        <v>5.18</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.73</v>
+        <v>1.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.11</v>
+        <v>7.1</v>
       </c>
       <c r="R66" t="n">
-        <v>5.18</v>
+        <v>13</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,16 +13454,16 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R68" t="n">
-        <v>3.29</v>
+        <v>2.36</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>2.65</v>
+        <v>3.29</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.11</v>
+        <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>4.59</v>
+        <v>12.6</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="R80" t="n">
-        <v>3.14</v>
+        <v>1.68</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,16 +16212,16 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17006,10 +17006,10 @@
         <v>0</v>
       </c>
       <c r="AG84" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.9</v>
+        <v>3.62</v>
       </c>
       <c r="R85" t="n">
-        <v>3.02</v>
+        <v>2.4</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.49</v>
+        <v>1.74</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.27</v>
+        <v>3.78</v>
       </c>
       <c r="R90" t="n">
-        <v>2.99</v>
+        <v>3.84</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R92" t="n">
-        <v>3.2</v>
+        <v>5.86</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.83</v>
+        <v>7.65</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="R93" t="n">
-        <v>4.22</v>
+        <v>1.48</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.04</v>
+        <v>1.83</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.44</v>
+        <v>3.87</v>
       </c>
       <c r="R94" t="n">
-        <v>2.53</v>
+        <v>4.22</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.69</v>
+        <v>3.04</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="R103" t="n">
-        <v>5.86</v>
+        <v>2.53</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R122" t="n">
-        <v>2.44</v>
+        <v>3.7</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="R123" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R124" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q164" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="R167" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q168" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="R168" t="n">
-        <v>3.86</v>
+        <v>3.59</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.92</v>
+        <v>3.76</v>
       </c>
       <c r="R169" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.74</v>
+        <v>2.7</v>
       </c>
       <c r="R172" t="n">
-        <v>3.51</v>
+        <v>3.86</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.76</v>
+        <v>2.92</v>
       </c>
       <c r="R173" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>8.199999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="Q174" t="n">
-        <v>5.73</v>
+        <v>4.72</v>
       </c>
       <c r="R174" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF174" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>6.49</v>
+        <v>2.36</v>
       </c>
       <c r="Q175" t="n">
-        <v>4.72</v>
+        <v>3.73</v>
       </c>
       <c r="R175" t="n">
-        <v>1.38</v>
+        <v>2.86</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.73</v>
+        <v>5.73</v>
       </c>
       <c r="R176" t="n">
-        <v>2.86</v>
+        <v>1.32</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36257,7 +36257,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.53</v>
+        <v>3.11</v>
       </c>
       <c r="R183" t="n">
-        <v>5.9</v>
+        <v>2.51</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="Q192" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="R192" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="R193" t="n">
-        <v>4.62</v>
+        <v>3.61</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF193" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.8</v>
+        <v>5.43</v>
       </c>
       <c r="R194" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AF194" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="R195" t="n">
-        <v>3.61</v>
+        <v>4.62</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="Q196" t="n">
-        <v>5.43</v>
+        <v>3.8</v>
       </c>
       <c r="R196" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AF196" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>7.46</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39267,10 +39267,10 @@
         <v>0</v>
       </c>
       <c r="AG197" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH197" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI197" t="n">
         <v>0</v>
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>7.46</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39661,10 +39661,10 @@
         <v>0</v>
       </c>
       <c r="AG199" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH199" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q202" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40246,10 +40246,10 @@
         <v>0</v>
       </c>
       <c r="AE202" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF202" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG202" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,22 +40941,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>2.33</v>
+        <v>1.22</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="R206" t="n">
-        <v>3.02</v>
+        <v>11.5</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41040,10 +41040,10 @@
         <v>0</v>
       </c>
       <c r="AG206" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH206" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>2.6</v>
+        <v>6.29</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="R207" t="n">
-        <v>2.66</v>
+        <v>1.53</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>1.09</v>
+        <v>2.33</v>
       </c>
       <c r="Q209" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="R209" t="n">
-        <v>22</v>
+        <v>3.02</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41631,10 +41631,10 @@
         <v>0</v>
       </c>
       <c r="AG209" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH209" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI209" t="n">
         <v>0</v>
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.79</v>
+        <v>1.09</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.52</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R210" t="n">
-        <v>4.47</v>
+        <v>22</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>10.1</v>
+        <v>1.79</v>
       </c>
       <c r="Q211" t="n">
-        <v>5.35</v>
+        <v>3.52</v>
       </c>
       <c r="R211" t="n">
-        <v>1.28</v>
+        <v>4.47</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>6.29</v>
+        <v>10.1</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.92</v>
+        <v>5.35</v>
       </c>
       <c r="R214" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42807,10 +42807,10 @@
         <v>0</v>
       </c>
       <c r="AE215" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF215" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG215" t="n">
         <v>0</v>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.96</v>
+        <v>1.42</v>
       </c>
       <c r="Q218" t="n">
-        <v>3.38</v>
+        <v>4.86</v>
       </c>
       <c r="R218" t="n">
-        <v>3.83</v>
+        <v>9.4</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF218" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.21</v>
+        <v>3.32</v>
       </c>
       <c r="R221" t="n">
-        <v>3.89</v>
+        <v>2.67</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43989,10 +43989,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF221" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q222" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="R223" t="n">
-        <v>3.64</v>
+        <v>3.91</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AF223" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="R224" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF224" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="Q225" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R225" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44777,10 +44777,10 @@
         <v>0</v>
       </c>
       <c r="AE225" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF225" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG225" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>2.69</v>
+        <v>1.31</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.32</v>
+        <v>5.98</v>
       </c>
       <c r="R226" t="n">
-        <v>2.67</v>
+        <v>8.65</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,16 +44974,16 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF226" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG226" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH226" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI226" t="n">
         <v>0</v>
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>1.89</v>
+        <v>3.44</v>
       </c>
       <c r="Q227" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="R227" t="n">
-        <v>3.91</v>
+        <v>2.09</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AF227" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>2.99</v>
+        <v>2.11</v>
       </c>
       <c r="Q228" t="n">
-        <v>3.46</v>
+        <v>3.21</v>
       </c>
       <c r="R228" t="n">
-        <v>2.36</v>
+        <v>3.89</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45368,10 +45368,10 @@
         <v>0</v>
       </c>
       <c r="AE228" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF228" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1.31</v>
+        <v>2.03</v>
       </c>
       <c r="Q230" t="n">
-        <v>5.98</v>
+        <v>3.59</v>
       </c>
       <c r="R230" t="n">
-        <v>8.65</v>
+        <v>3.64</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,16 +45762,16 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF230" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG230" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q231" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -45959,10 +45959,10 @@
         <v>0</v>
       </c>
       <c r="AE231" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF231" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
@@ -46063,22 +46063,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q233" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="R234" t="n">
-        <v>3.06</v>
+        <v>4.24</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF234" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="Q235" t="n">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47141,10 +47141,10 @@
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF237" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG237" t="n">
         <v>0</v>
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>1.15</v>
+        <v>5.64</v>
       </c>
       <c r="Q241" t="n">
-        <v>7.85</v>
+        <v>3.98</v>
       </c>
       <c r="R241" t="n">
-        <v>10.5</v>
+        <v>1.49</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>5.64</v>
+        <v>1.15</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.98</v>
+        <v>7.85</v>
       </c>
       <c r="R242" t="n">
-        <v>1.49</v>
+        <v>10.5</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>3.94</v>
+        <v>2.22</v>
       </c>
       <c r="Q243" t="n">
-        <v>4.11</v>
+        <v>3.1</v>
       </c>
       <c r="R243" t="n">
-        <v>1.93</v>
+        <v>3.32</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q244" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF244" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF249" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF250" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q252" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF252" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF257" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51278,10 +51278,10 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF258" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51475,10 +51475,10 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF259" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51672,10 +51672,10 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF260" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.44</v>
+        <v>2.85</v>
       </c>
       <c r="R261" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -51869,10 +51869,10 @@
         <v>0</v>
       </c>
       <c r="AE261" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AF261" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AG261" t="n">
         <v>0</v>
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>5.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q263" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R263" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52263,10 +52263,10 @@
         <v>0</v>
       </c>
       <c r="AE263" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF263" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG263" t="n">
         <v>0</v>
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,55 +52415,55 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>3.4</v>
+        <v>5.26</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R264" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" t="n">
+        <v>0</v>
+      </c>
+      <c r="V264" t="n">
+        <v>0</v>
+      </c>
+      <c r="W264" t="n">
+        <v>0</v>
+      </c>
+      <c r="X264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF264" t="n">
         <v>2.05</v>
-      </c>
-      <c r="S264" t="n">
-        <v>0</v>
-      </c>
-      <c r="T264" t="n">
-        <v>0</v>
-      </c>
-      <c r="U264" t="n">
-        <v>0</v>
-      </c>
-      <c r="V264" t="n">
-        <v>0</v>
-      </c>
-      <c r="W264" t="n">
-        <v>0</v>
-      </c>
-      <c r="X264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE264" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF264" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53203,13 +53203,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q268" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53400,13 +53400,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q269" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q271" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q276" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54824,10 +54824,10 @@
         <v>0</v>
       </c>
       <c r="AE276" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF276" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG276" t="n">
         <v>0</v>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55021,10 +55021,10 @@
         <v>0</v>
       </c>
       <c r="AE277" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF277" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55567,13 +55567,13 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q280" t="n">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="R280" t="n">
-        <v>2.67</v>
+        <v>5.19</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -55612,10 +55612,10 @@
         <v>0</v>
       </c>
       <c r="AE280" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF280" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG280" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="Q281" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="R281" t="n">
-        <v>5.19</v>
+        <v>2.67</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55809,10 +55809,10 @@
         <v>0</v>
       </c>
       <c r="AE281" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF281" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG281" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF283" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>3.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R284" t="n">
-        <v>2.05</v>
+        <v>5.15</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56400,16 +56400,16 @@
         <v>0</v>
       </c>
       <c r="AE284" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF284" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG284" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH284" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI284" t="n">
         <v>0</v>
@@ -56504,7 +56504,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56597,10 +56597,10 @@
         <v>0</v>
       </c>
       <c r="AE285" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF285" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG285" t="n">
         <v>0</v>
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q286" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56800,10 +56800,10 @@
         <v>0</v>
       </c>
       <c r="AG286" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH286" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI286" t="n">
         <v>0</v>
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q287" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -56991,10 +56991,10 @@
         <v>0</v>
       </c>
       <c r="AE287" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF287" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG287" t="n">
         <v>0</v>

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>3.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
-        <v>8.4</v>
+        <v>1.76</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.91</v>
+        <v>34</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.12</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>3.62</v>
+        <v>1.02</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="R54" t="n">
-        <v>4.39</v>
+        <v>1.32</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>34</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="R55" t="n">
-        <v>1.02</v>
+        <v>4.39</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="R58" t="n">
-        <v>2.53</v>
+        <v>3.21</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.72</v>
+        <v>2.82</v>
       </c>
       <c r="R61" t="n">
-        <v>10.7</v>
+        <v>2.53</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.05</v>
+        <v>1.34</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.32</v>
+        <v>5.72</v>
       </c>
       <c r="R62" t="n">
-        <v>3.21</v>
+        <v>10.7</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="Q66" t="n">
-        <v>7.1</v>
+        <v>4.11</v>
       </c>
       <c r="R66" t="n">
-        <v>13</v>
+        <v>5.18</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,16 +13454,16 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>2.65</v>
+        <v>3.29</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>3.29</v>
+        <v>2.65</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>3.11</v>
       </c>
       <c r="R75" t="n">
-        <v>12.6</v>
+        <v>4.59</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.82</v>
+        <v>1.26</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>3.65</v>
+        <v>12.6</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="R79" t="n">
-        <v>3.02</v>
+        <v>4.09</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.2</v>
+        <v>1.82</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>1.68</v>
+        <v>3.65</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="R86" t="n">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.74</v>
+        <v>2.52</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="R90" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.08</v>
+        <v>3.87</v>
       </c>
       <c r="R91" t="n">
-        <v>3.89</v>
+        <v>4.22</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.69</v>
+        <v>3.8</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="R92" t="n">
-        <v>5.86</v>
+        <v>1.8</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.83</v>
+        <v>3.04</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.87</v>
+        <v>3.44</v>
       </c>
       <c r="R94" t="n">
-        <v>4.22</v>
+        <v>2.53</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2</v>
+        <v>3.21</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.48</v>
+        <v>3.27</v>
       </c>
       <c r="R98" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R107" t="n">
-        <v>1.8</v>
+        <v>5.86</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="R109" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.44</v>
+        <v>2.47</v>
       </c>
       <c r="Q110" t="n">
-        <v>4.96</v>
+        <v>3.35</v>
       </c>
       <c r="R110" t="n">
-        <v>8.25</v>
+        <v>2.65</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="R114" t="n">
-        <v>2.44</v>
+        <v>3.89</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="R119" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R120" t="n">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.44</v>
+        <v>4.96</v>
       </c>
       <c r="R121" t="n">
-        <v>3.89</v>
+        <v>8.25</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R123" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="R124" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.28</v>
+        <v>3.76</v>
       </c>
       <c r="R168" t="n">
-        <v>3.59</v>
+        <v>2.66</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.76</v>
+        <v>2.92</v>
       </c>
       <c r="R169" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="Q170" t="n">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="R170" t="n">
-        <v>4.37</v>
+        <v>3.51</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q173" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="R173" t="n">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>6.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q174" t="n">
-        <v>4.72</v>
+        <v>5.73</v>
       </c>
       <c r="R174" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF174" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.36</v>
+        <v>6.49</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.73</v>
+        <v>4.72</v>
       </c>
       <c r="R175" t="n">
-        <v>2.86</v>
+        <v>1.38</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF176" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF179" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35912,10 +35912,10 @@
         <v>0</v>
       </c>
       <c r="AE180" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF180" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF181" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36454,17 +36454,17 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q191" t="n">
-        <v>4.53</v>
+        <v>3.28</v>
       </c>
       <c r="R191" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.03</v>
+        <v>1.39</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.3</v>
+        <v>5.43</v>
       </c>
       <c r="R193" t="n">
-        <v>3.61</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q194" t="n">
-        <v>5.43</v>
+        <v>3.19</v>
       </c>
       <c r="R194" t="n">
-        <v>8.800000000000001</v>
+        <v>4.62</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AF194" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.19</v>
+        <v>3.8</v>
       </c>
       <c r="R195" t="n">
-        <v>4.62</v>
+        <v>3.8</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R196" t="n">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q199" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>7.46</v>
+        <v>0</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39661,10 +39661,10 @@
         <v>0</v>
       </c>
       <c r="AG199" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH199" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI199" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39852,10 +39852,10 @@
         <v>0</v>
       </c>
       <c r="AE200" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF200" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG200" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>7.46</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40252,10 +40252,10 @@
         <v>0</v>
       </c>
       <c r="AG202" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH202" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI202" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF203" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -41138,22 +41138,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>6.29</v>
+        <v>2.33</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="R207" t="n">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41237,10 +41237,10 @@
         <v>0</v>
       </c>
       <c r="AG207" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH207" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>2.33</v>
+        <v>6.29</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="R209" t="n">
-        <v>3.02</v>
+        <v>1.53</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41631,10 +41631,10 @@
         <v>0</v>
       </c>
       <c r="AG209" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH209" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.79</v>
+        <v>10.1</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.52</v>
+        <v>5.35</v>
       </c>
       <c r="R211" t="n">
-        <v>4.47</v>
+        <v>1.28</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42320,22 +42320,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42413,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="AE213" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF213" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q214" t="n">
-        <v>5.35</v>
+        <v>3.14</v>
       </c>
       <c r="R214" t="n">
-        <v>1.28</v>
+        <v>2.66</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,22 +42714,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="Q215" t="n">
-        <v>4.21</v>
+        <v>4.86</v>
       </c>
       <c r="R215" t="n">
-        <v>4.83</v>
+        <v>9.4</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42807,10 +42807,10 @@
         <v>0</v>
       </c>
       <c r="AE215" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AF215" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AG215" t="n">
         <v>0</v>
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.86</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R218" t="n">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF218" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>3.42</v>
+        <v>1.31</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.1</v>
+        <v>5.98</v>
       </c>
       <c r="R220" t="n">
-        <v>2.17</v>
+        <v>8.65</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43798,10 +43798,10 @@
         <v>0</v>
       </c>
       <c r="AG220" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH220" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI220" t="n">
         <v>0</v>
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>2.69</v>
+        <v>3.44</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="R221" t="n">
-        <v>2.67</v>
+        <v>2.09</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -43989,10 +43989,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AF221" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>2.55</v>
+        <v>3.42</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R222" t="n">
-        <v>2.93</v>
+        <v>2.17</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44186,10 +44186,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>1.89</v>
+        <v>2.69</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.83</v>
+        <v>3.32</v>
       </c>
       <c r="R223" t="n">
-        <v>3.91</v>
+        <v>2.67</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AF223" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44535,13 +44535,13 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>2.99</v>
+        <v>1.89</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.46</v>
+        <v>3.83</v>
       </c>
       <c r="R224" t="n">
-        <v>2.36</v>
+        <v>3.91</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -44580,10 +44580,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AF224" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>1.31</v>
+        <v>2.55</v>
       </c>
       <c r="Q226" t="n">
-        <v>5.98</v>
+        <v>3.2</v>
       </c>
       <c r="R226" t="n">
-        <v>8.65</v>
+        <v>2.93</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -44974,16 +44974,16 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG226" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI226" t="n">
         <v>0</v>
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="Q227" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="R227" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AF227" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q228" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.59</v>
+        <v>3.21</v>
       </c>
       <c r="R230" t="n">
-        <v>3.64</v>
+        <v>3.89</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45762,10 +45762,10 @@
         <v>0</v>
       </c>
       <c r="AE230" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF230" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>2.17</v>
+        <v>6.49</v>
       </c>
       <c r="Q234" t="n">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="R234" t="n">
-        <v>4.24</v>
+        <v>1.5</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF234" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>6.49</v>
+        <v>10.6</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.7</v>
+        <v>6.02</v>
       </c>
       <c r="R236" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -46944,10 +46944,10 @@
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF236" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG236" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q238" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>10.6</v>
+        <v>3.41</v>
       </c>
       <c r="Q239" t="n">
-        <v>6.02</v>
+        <v>3.13</v>
       </c>
       <c r="R239" t="n">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>2.22</v>
+        <v>3.94</v>
       </c>
       <c r="Q243" t="n">
-        <v>3.1</v>
+        <v>4.11</v>
       </c>
       <c r="R243" t="n">
-        <v>3.32</v>
+        <v>1.93</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF243" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>3.94</v>
+        <v>2.22</v>
       </c>
       <c r="Q244" t="n">
-        <v>4.11</v>
+        <v>3.1</v>
       </c>
       <c r="R244" t="n">
-        <v>1.93</v>
+        <v>3.32</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF249" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q250" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="R250" t="n">
-        <v>3.45</v>
+        <v>3.69</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF250" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,13 +49854,13 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="Q252" t="n">
-        <v>3.44</v>
+        <v>2.85</v>
       </c>
       <c r="R252" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AF252" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="Q255" t="n">
-        <v>3.18</v>
+        <v>3.86</v>
       </c>
       <c r="R255" t="n">
-        <v>3.69</v>
+        <v>4.29</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50687,10 +50687,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF255" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51081,10 +51081,10 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF257" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG257" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q260" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51672,10 +51672,10 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF260" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q261" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -51869,10 +51869,10 @@
         <v>0</v>
       </c>
       <c r="AE261" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF261" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG261" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52809,13 +52809,13 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q266" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S266" t="n">
         <v>0</v>
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53400,13 +53400,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q269" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q276" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54824,10 +54824,10 @@
         <v>0</v>
       </c>
       <c r="AE276" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF276" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG276" t="n">
         <v>0</v>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q279" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55415,10 +55415,10 @@
         <v>0</v>
       </c>
       <c r="AE279" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF279" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG279" t="n">
         <v>0</v>
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55567,13 +55567,13 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="Q280" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="R280" t="n">
-        <v>5.19</v>
+        <v>2.67</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -55612,10 +55612,10 @@
         <v>0</v>
       </c>
       <c r="AE280" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF280" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG280" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q281" t="n">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="R281" t="n">
-        <v>2.67</v>
+        <v>5.19</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55809,10 +55809,10 @@
         <v>0</v>
       </c>
       <c r="AE281" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF281" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG281" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1.6</v>
+        <v>3.24</v>
       </c>
       <c r="Q283" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R283" t="n">
-        <v>6.25</v>
+        <v>2.05</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56203,10 +56203,10 @@
         <v>0</v>
       </c>
       <c r="AE283" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AF283" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AG283" t="n">
         <v>0</v>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56355,13 +56355,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q284" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -56406,10 +56406,10 @@
         <v>0</v>
       </c>
       <c r="AG284" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH284" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI284" t="n">
         <v>0</v>
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56749,13 +56749,13 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q286" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -56800,10 +56800,10 @@
         <v>0</v>
       </c>
       <c r="AG286" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH286" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI286" t="n">
         <v>0</v>
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>3.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q287" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R287" t="n">
-        <v>2.05</v>
+        <v>6.25</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -56991,10 +56991,10 @@
         <v>0</v>
       </c>
       <c r="AE287" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AF287" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AG287" t="n">
         <v>0</v>
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G292" t="n">

--- a/jogos_2026-03-22.xlsx
+++ b/jogos_2026-03-22.xlsx
@@ -1344,22 +134